--- a/boardAPI.xlsx
+++ b/boardAPI.xlsx
@@ -62,7 +62,9 @@
   </si>
   <si>
     <t>{
-   category:string
+   category:string,
+   page:number,
+   board_limit:number
 }</t>
   </si>
   <si>
@@ -72,7 +74,9 @@
     nick:string,
     createdAt:string,
     looks:number,
-    recommend:number
+    cmtCnt:number,
+    recommend:number,
+    boardCnt:number
 }</t>
   </si>
 </sst>
@@ -427,7 +431,7 @@
     <col customWidth="1" min="3" max="3" width="7.25"/>
     <col customWidth="1" min="4" max="4" width="6.13"/>
     <col customWidth="1" min="5" max="5" width="8.25"/>
-    <col customWidth="1" min="6" max="6" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="16.63"/>
     <col customWidth="1" min="7" max="7" width="28.38"/>
     <col customWidth="1" min="8" max="8" width="8.5"/>
     <col customWidth="1" min="9" max="9" width="23.75"/>

--- a/boardAPI.xlsx
+++ b/boardAPI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -25,7 +25,10 @@
     <t>Response</t>
   </si>
   <si>
-    <t>Info</t>
+    <t>session</t>
+  </si>
+  <si>
+    <t>info</t>
   </si>
   <si>
     <t>비고</t>
@@ -52,10 +55,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>main_get</t>
-  </si>
-  <si>
-    <t>/board</t>
+    <t>board_list_get</t>
+  </si>
+  <si>
+    <t>/board/board</t>
   </si>
   <si>
     <t>get</t>
@@ -69,15 +72,71 @@
   </si>
   <si>
     <t>{
-    id:number,
-    title:string,
-    nick:string,
-    createdAt:string,
-    looks:number,
-    cmtCnt:number,
-    recommend:number,
+    boards:Array&lt;
+                           {
+                           id:number,
+                           title:string,
+                           nick:string,
+                           createdAt:string,
+                           looks:number,
+                           cmtCnt:number,
+                           recommend:number,
+                           categoryTitle:string,
+                           categoryHref:string
+                           }
+                        &gt;,
     boardCnt:number
 }</t>
+  </si>
+  <si>
+    <t>category_list_get</t>
+  </si>
+  <si>
+    <t>{
+    categories:Array&lt;
+                                 {
+                                  title:string,
+                                  href:string
+                                 }
+                               &gt;
+}</t>
+  </si>
+  <si>
+    <t>user_personal_get</t>
+  </si>
+  <si>
+    <t>{
+   strId:string,
+   pwd:string
+}</t>
+  </si>
+  <si>
+    <t>{
+   id:number,
+   nick:string
+   strId:string,   
+}</t>
+  </si>
+  <si>
+    <t>user_personal_post</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>{
+   nick:string,
+   strId:string,
+   pwd:string
+}</t>
+  </si>
+  <si>
+    <t>{
+   response:"ok"
+}</t>
+  </si>
+  <si>
+    <t>응답 데이터는 임시로 지정, 추후 변경 가능</t>
   </si>
 </sst>
 </file>
@@ -182,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -194,6 +253,12 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -212,6 +277,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,7 +497,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.25"/>
+    <col customWidth="1" min="1" max="1" width="15.63"/>
     <col customWidth="1" min="2" max="2" width="17.38"/>
     <col customWidth="1" min="3" max="3" width="7.25"/>
     <col customWidth="1" min="4" max="4" width="6.13"/>
@@ -436,8 +507,9 @@
     <col customWidth="1" min="8" max="8" width="8.5"/>
     <col customWidth="1" min="9" max="9" width="23.75"/>
     <col customWidth="1" min="10" max="10" width="5.75"/>
-    <col customWidth="1" min="11" max="11" width="28.25"/>
+    <col customWidth="1" min="11" max="11" width="28.38"/>
     <col customWidth="1" min="13" max="13" width="34.25"/>
+    <col customWidth="1" min="14" max="14" width="32.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -460,89 +532,189 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>5</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="I2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="9">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11">
         <v>200.0</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
+      <c r="K3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="14">
+        <v>200.0</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="14">
+        <v>204.0</v>
+      </c>
+      <c r="K5" s="15"/>
+      <c r="L5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="14">
+        <v>201.0</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+    </row>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1"/>
@@ -1522,13 +1694,14 @@
     <row r="983" ht="15.75" customHeight="1"/>
     <row r="984" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
